--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\PJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFD5458-B75D-4F0A-AA95-144212090B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850DAAC6-368F-43D9-97A6-00F5F8290A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Songs" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="171">
   <si>
     <t>index</t>
   </si>
@@ -528,13 +528,33 @@
   </si>
   <si>
     <t>Abracadabra</t>
+  </si>
+  <si>
+    <r>
+      <t>ノンブレス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・オブリージュ</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>논브레스 오블리주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -548,6 +568,13 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -844,7 +871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2965,6 +2992,29 @@
       </c>
       <c r="G92">
         <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>1092</v>
+      </c>
+      <c r="B93">
+        <v>2092</v>
+      </c>
+      <c r="C93" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93">
+        <v>26</v>
+      </c>
+      <c r="E93">
+        <v>20</v>
+      </c>
+      <c r="F93">
+        <v>14</v>
+      </c>
+      <c r="G93">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2978,7 +3028,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C93"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -3919,6 +3969,17 @@
         <v>168</v>
       </c>
     </row>
+    <row r="93" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A93">
+        <v>2092</v>
+      </c>
+      <c r="B93" t="s">
+        <v>169</v>
+      </c>
+      <c r="C93" t="s">
+        <v>170</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
